--- a/data/NYSERDA_DER_Portfolio_Metric_Data_org.xlsx
+++ b/data/NYSERDA_DER_Portfolio_Metric_Data_org.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangseohyun/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangseohyun/SynologyDrive/workspace/symply/DER/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0516F5D-08A5-E647-A2DD-019F187C9805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27743720-CA12-AB45-A6A4-B08C163F6C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="4940" windowWidth="20600" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36560" yWindow="-880" windowWidth="20600" windowHeight="21440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facilities" sheetId="1" r:id="rId1"/>
@@ -1450,10 +1450,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3848,7 +3847,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="2">
+      <c r="A81">
         <v>524</v>
       </c>
       <c r="B81" t="s">
@@ -4108,7 +4107,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="2">
+      <c r="A91">
         <v>692</v>
       </c>
       <c r="B91" t="s">
